--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE IGNIÇÃO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE IGNIÇÃO - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,269 +1653,6 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7908073710464</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE SMARTFOX TITAN FAN160/ CB250F TWISTER 2016</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>7895099120189</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE IRON YBR125 2005 A 2007/ XTZ125 2002 A 2016/ FACTOR125/ FAZER 2013 A 2019/ XTZ250 027463</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>7908073725741</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE SMARTFOX XTZ150 2014</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7895099122473</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE IRON BIZ125 2009/ FAN125 2009 028358</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>602883766563</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CI IRON JET50 2014 017741</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3905000018314</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE SOLIDEZ C100 DREAM 1990 A 1997 39050</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>39001</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE SOLIDEZ JET50 2014</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>6974288493394</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE BRAVIC NXR160/ FAN125/ XRE190/ XRE300 BMA63004</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7895099122237</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE IRON CB300 2012 A 2021/ XRE300 2009 A 2012/ TITAN CG 2004 A 2008/ FAN150 START/ FALCON/ CBX250 027462</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7898751860904</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE EXTREMO BIZ125 2011/ BIZ100 2013</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>6942234809162</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TAMPA TANQUE BRAVIC YES125 BMA 63010</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE IGNIÇÃO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE IGNIÇÃO - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -649,17 +604,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO IRON NXR160 2018 A 2019 201376</t>
+          <t>CHAVE IGNIÇÃO IRON BROS NXR160 2018 A 2019 201376</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
     </row>
@@ -682,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -774,7 +704,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO BRAVCHAVE IGNIÇÃO C/ TAMPA PCX150 BMA69011</t>
+          <t>CHAVE IGNIÇÃO BRAVIC / TAMPA PCX150 BMA69011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -782,7 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -803,11 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -828,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -845,7 +764,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO BRAVCHAVE IGNIÇÃO C/ TAMPA PCX150 2019615</t>
+          <t>CHAVE IGNIÇÃO BRAVIC C/ TAMPA PCX150 2019615</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -853,7 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -874,11 +792,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -891,15 +804,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVE IGNIÇÃO CATIIMTO DAFRA RIVA </t>
+          <t xml:space="preserve">CHAVE IGNIÇÃO CATIIMOTO DAFRA RIVA150 </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -920,11 +832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -945,11 +852,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -970,11 +872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -991,11 +888,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1016,11 +908,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1041,11 +928,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1066,7 +948,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1087,11 +968,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1112,11 +988,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1137,7 +1008,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1158,11 +1028,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1183,11 +1048,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1208,11 +1068,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1233,7 +1088,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1254,7 +1108,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1275,11 +1128,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1300,7 +1148,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1321,11 +1168,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1346,11 +1188,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1363,17 +1200,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO IRON NXR150 2011 A 2014 201367</t>
+          <t>CHAVE IGNIÇÃO IRON BROS NXR150 2011 A 2014 201367</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
     </row>
@@ -1396,11 +1228,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1421,11 +1248,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1446,7 +1268,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1459,7 +1280,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO BRAVCHAVE IGNIÇÃO C/ TAMPA CB300 BMA69003</t>
+          <t>CHAVE IGNIÇÃO BRAVIC C/ TAMPA CB300 BMA69003</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1467,7 +1288,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1488,7 +1308,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1509,7 +1328,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1522,7 +1340,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHAVE IGNIÇÃO BRAVCHAVE IGNIÇÃO C/ TAMPA TITANFAN CG150 2009 A 2013 KS BMA69028</t>
+          <t>CHAVE IGNIÇÃO BRAVIC C/ TAMPA TITAN FAN CG150 2009 A 2013 KS BMA69028</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1530,7 +1348,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1551,7 +1368,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1572,11 +1388,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1597,11 +1408,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1622,11 +1428,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1647,9 +1448,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>35</t>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7895099120103</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CHAVE INGNIÇAO IRON XTZ125 2006 A 2008 027459</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
